--- a/artfynd/A 51326-2024 artfynd.xlsx
+++ b/artfynd/A 51326-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>87510699</v>
       </c>
       <c r="B2" t="n">
-        <v>5107</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -736,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558345.2188092802</v>
+        <v>558345</v>
       </c>
       <c r="R2" t="n">
-        <v>6572992.664043128</v>
+        <v>6572993</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -769,19 +764,9 @@
           <t>2020-07-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-07-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -812,12 +797,7 @@
         <v>97688360</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -849,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558255.2845870957</v>
+        <v>558255</v>
       </c>
       <c r="R3" t="n">
-        <v>6572949.898498183</v>
+        <v>6572950</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -882,19 +862,9 @@
           <t>1980-08-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1980-08-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,6 +893,108 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>97688361</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lindhagen, 1 km SV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>558442</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6572904</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Västermo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1980-08-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1980-08-20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>blandskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51326-2024 artfynd.xlsx
+++ b/artfynd/A 51326-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87510699</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97688360</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,8 +1010,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97688361</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>